--- a/data/trans_dic/P36$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,78</t>
+          <t>1,72; 3,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,79</t>
+          <t>1,62; 3,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,71</t>
+          <t>0,73; 2,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,87</t>
+          <t>0,67; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,31</t>
+          <t>0,29; 1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,21</t>
+          <t>0,19; 1,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,38</t>
+          <t>1,29; 2,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,09</t>
+          <t>0,99; 2,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,52</t>
+          <t>0,57; 1,51</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,73</t>
+          <t>1,4; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,54</t>
+          <t>1,91; 3,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,11</t>
+          <t>1,71; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,65</t>
+          <t>1,33; 2,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,73</t>
+          <t>2,03; 3,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,04</t>
+          <t>0,98; 2,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,5</t>
+          <t>1,53; 2,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,44</t>
+          <t>2,27; 3,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,32</t>
+          <t>1,5; 2,35</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,41</t>
+          <t>0,51; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,42</t>
+          <t>1,02; 4,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,42</t>
+          <t>0,35; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,11</t>
+          <t>0,72; 3,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,49</t>
+          <t>0,84; 2,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,45</t>
+          <t>0,71; 2,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,3</t>
+          <t>0,24; 1,2</t>
         </is>
       </c>
     </row>
@@ -1008,27 +1008,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,63</t>
+          <t>1,59; 2,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,28</t>
+          <t>2,03; 3,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,45</t>
+          <t>1,44; 2,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,03</t>
+          <t>1,17; 2,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,22</t>
+          <t>1,34; 2,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,21</t>
+          <t>1,53; 2,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,56</t>
+          <t>1,81; 2,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,77</t>
+          <t>1,15; 1,76</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18437; 38849</t>
+          <t>17703; 39289</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14948; 36865</t>
+          <t>15741; 37699</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5248; 20365</t>
+          <t>5522; 19830</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8220; 24517</t>
+          <t>8768; 25200</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4075; 17528</t>
+          <t>3892; 16968</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2036; 12064</t>
+          <t>1925; 11647</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29803; 55647</t>
+          <t>30247; 55864</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22274; 48222</t>
+          <t>22806; 47847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9635; 26463</t>
+          <t>9951; 26430</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24055; 46138</t>
+          <t>23731; 45124</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38862; 69422</t>
+          <t>37385; 70123</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34319; 64446</t>
+          <t>35541; 64209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20636; 42077</t>
+          <t>21118; 42055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36495; 65413</t>
+          <t>35681; 65772</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19329; 40428</t>
+          <t>19545; 40294</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50681; 82063</t>
+          <t>50228; 81451</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82507; 127730</t>
+          <t>84475; 127995</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59346; 94291</t>
+          <t>60920; 95397</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2758; 13239</t>
+          <t>2819; 13931</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4963; 21207</t>
+          <t>4896; 19964</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1978; 13246</t>
+          <t>1912; 13108</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3138; 14834</t>
+          <t>3418; 15343</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6284</t>
+          <t>0; 6911</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4756</t>
+          <t>0; 5114</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8611; 25503</t>
+          <t>8656; 24431</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6706; 22977</t>
+          <t>6636; 22782</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2798; 14204</t>
+          <t>2635; 13105</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>53617; 86118</t>
+          <t>52059; 85648</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70241; 111872</t>
+          <t>69274; 111172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48894; 82576</t>
+          <t>48676; 83476</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40235; 68593</t>
+          <t>39420; 69792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47358; 78880</t>
+          <t>47537; 80005</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25414; 48927</t>
+          <t>25397; 48899</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>100811; 146599</t>
+          <t>101491; 145377</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>126026; 177936</t>
+          <t>125832; 176501</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80045; 122383</t>
+          <t>79524; 121193</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$nada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Estudios-trans_dic.xlsx
@@ -678,42 +678,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,82</t>
+          <t>1,71; 3,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,88</t>
+          <t>1,69; 3,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,63</t>
+          <t>0,77; 2,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,66; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,27</t>
+          <t>0,31; 1,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,17</t>
+          <t>0,21; 1,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,39</t>
+          <t>1,31; 2,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,07</t>
+          <t>1,01; 2,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 2,67</t>
+          <t>1,42; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,58</t>
+          <t>1,92; 3,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,1</t>
+          <t>1,67; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,65</t>
+          <t>1,33; 2,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,75</t>
+          <t>2,1; 3,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,03</t>
+          <t>0,96; 2,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,48</t>
+          <t>1,54; 2,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,44</t>
+          <t>2,22; 3,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,35</t>
+          <t>1,55; 2,4</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,53</t>
+          <t>0,51; 2,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,16</t>
+          <t>1,04; 4,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,4</t>
+          <t>0,34; 2,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,22</t>
+          <t>0,72; 3,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,38</t>
+          <t>0,82; 2,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,43</t>
+          <t>0,72; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,2</t>
+          <t>0,25; 1,21</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,62</t>
+          <t>1,6; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,26</t>
+          <t>2,03; 3,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,47</t>
+          <t>1,45; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,07</t>
+          <t>1,22; 2,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,25</t>
+          <t>1,31; 2,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,39</t>
+          <t>0,7; 1,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,19</t>
+          <t>1,53; 2,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,54</t>
+          <t>1,81; 2,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,76</t>
+          <t>1,17; 1,76</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17703; 39289</t>
+          <t>17604; 38002</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15741; 37699</t>
+          <t>16469; 38209</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5522; 19830</t>
+          <t>5776; 20681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8768; 25200</t>
+          <t>8615; 24377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3892; 16968</t>
+          <t>4151; 17366</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1925; 11647</t>
+          <t>2105; 12411</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30247; 55864</t>
+          <t>30678; 56287</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22806; 47847</t>
+          <t>23326; 47780</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9951; 26430</t>
+          <t>9892; 26430</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23731; 45124</t>
+          <t>24060; 46346</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37385; 70123</t>
+          <t>37609; 71976</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35541; 64209</t>
+          <t>34704; 63807</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21118; 42055</t>
+          <t>21146; 41919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35681; 65772</t>
+          <t>36898; 66325</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19545; 40294</t>
+          <t>19106; 40273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50228; 81451</t>
+          <t>50540; 81573</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84475; 127995</t>
+          <t>82627; 126269</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60920; 95397</t>
+          <t>62818; 97636</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2819; 13931</t>
+          <t>2799; 14003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4896; 19964</t>
+          <t>4971; 21642</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1912; 13108</t>
+          <t>1884; 12137</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3418; 15343</t>
+          <t>3425; 16460</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6911</t>
+          <t>0; 6013</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5114</t>
+          <t>0; 6294</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8656; 24431</t>
+          <t>8414; 24625</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6636; 22782</t>
+          <t>6768; 24535</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2635; 13105</t>
+          <t>2789; 13218</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52059; 85648</t>
+          <t>52434; 84976</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69274; 111172</t>
+          <t>69255; 112381</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48676; 83476</t>
+          <t>48955; 82000</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39420; 69792</t>
+          <t>41150; 72259</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47537; 80005</t>
+          <t>46621; 80517</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25397; 48899</t>
+          <t>24729; 48978</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>101491; 145377</t>
+          <t>101631; 144151</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>125832; 176501</t>
+          <t>126014; 177581</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>79524; 121193</t>
+          <t>80555; 121522</t>
         </is>
       </c>
     </row>
